--- a/artfynd/A 10970-2025 artfynd.xlsx
+++ b/artfynd/A 10970-2025 artfynd.xlsx
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128472774</v>
+        <v>128472698</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>57833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,34 +1139,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Södra Lillterrsjö, Södra Lillterrsjö, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579834</v>
+        <v>579799</v>
       </c>
       <c r="R6" t="n">
-        <v>7058433</v>
+        <v>7058428</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128472698</v>
+        <v>128472774</v>
       </c>
       <c r="B7" t="n">
-        <v>57833</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,48 +1260,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Södra Lillterrsjö, Södra Lillterrsjö, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579799</v>
+        <v>579834</v>
       </c>
       <c r="R7" t="n">
-        <v>7058428</v>
+        <v>7058433</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128472805</v>
+        <v>128472792</v>
       </c>
       <c r="B8" t="n">
-        <v>57673</v>
+        <v>91356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,27 +1367,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1396,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579846</v>
+        <v>579831</v>
       </c>
       <c r="R8" t="n">
-        <v>7058444</v>
+        <v>7058436</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,12 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128472792</v>
+        <v>128472805</v>
       </c>
       <c r="B9" t="n">
-        <v>91356</v>
+        <v>57673</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,31 +1483,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1517,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579831</v>
+        <v>579846</v>
       </c>
       <c r="R9" t="n">
-        <v>7058436</v>
+        <v>7058444</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1557,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 10970-2025 artfynd.xlsx
+++ b/artfynd/A 10970-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128472722</v>
       </c>
       <c r="B2" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128472665</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128472655</v>
       </c>
       <c r="B4" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>128472740</v>
       </c>
       <c r="B5" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128472698</v>
       </c>
       <c r="B6" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>128472774</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128472792</v>
       </c>
       <c r="B8" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>128472805</v>
       </c>
       <c r="B9" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 10970-2025 artfynd.xlsx
+++ b/artfynd/A 10970-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128472722</v>
       </c>
       <c r="B2" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128472665</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128472655</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>128472740</v>
       </c>
       <c r="B5" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128472698</v>
       </c>
       <c r="B6" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>128472774</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128472792</v>
       </c>
       <c r="B8" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>128472805</v>
       </c>
       <c r="B9" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 10970-2025 artfynd.xlsx
+++ b/artfynd/A 10970-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>128472740</v>
       </c>
       <c r="B5" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128472792</v>
       </c>
       <c r="B8" t="n">
-        <v>91454</v>
+        <v>91460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 10970-2025 artfynd.xlsx
+++ b/artfynd/A 10970-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>128472740</v>
       </c>
       <c r="B5" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>128472774</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128472792</v>
       </c>
       <c r="B8" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 10970-2025 artfynd.xlsx
+++ b/artfynd/A 10970-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>128472740</v>
       </c>
       <c r="B5" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128472792</v>
       </c>
       <c r="B8" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 10970-2025 artfynd.xlsx
+++ b/artfynd/A 10970-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128472722</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128472665</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128472655</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>128472740</v>
       </c>
       <c r="B5" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128472698</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>128472774</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128472792</v>
       </c>
       <c r="B8" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>128472805</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 10970-2025 artfynd.xlsx
+++ b/artfynd/A 10970-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>128472740</v>
       </c>
       <c r="B5" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>128472774</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128472792</v>
       </c>
       <c r="B8" t="n">
-        <v>91490</v>
+        <v>91495</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 10970-2025 artfynd.xlsx
+++ b/artfynd/A 10970-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>128472740</v>
       </c>
       <c r="B5" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128472792</v>
       </c>
       <c r="B8" t="n">
-        <v>91495</v>
+        <v>91500</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 10970-2025 artfynd.xlsx
+++ b/artfynd/A 10970-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128472722</v>
       </c>
       <c r="B2" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128472665</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128472655</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>128472740</v>
       </c>
       <c r="B5" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128472698</v>
       </c>
       <c r="B6" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>128472774</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128472792</v>
       </c>
       <c r="B8" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>128472805</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 10970-2025 artfynd.xlsx
+++ b/artfynd/A 10970-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128472722</v>
       </c>
       <c r="B2" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128472665</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128472655</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>128472740</v>
       </c>
       <c r="B5" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128472698</v>
       </c>
       <c r="B6" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>128472774</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>128472792</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>128472805</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
